--- a/Libro1(Recuperado automáticamente).xlsx
+++ b/Libro1(Recuperado automáticamente).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CIST\Downloads\Selene-PFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{5E5DEA28-1CEC-4C44-A7BD-5E559EEC60D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37F084B-6C66-4D74-A006-2042BE022F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EBE5DF2-C0CF-4ED1-8D2B-CD3E00818B64}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="121">
   <si>
     <t>Como usuario, quiero buscar y descubrir música basada en mi perfil.</t>
   </si>
@@ -95,9 +94,6 @@
   </si>
   <si>
     <t>Como administrador, quiero validar automáticamente los contenidos ingeridos por infracción de derechos de autor.</t>
-  </si>
-  <si>
-    <t>Como administrador, quiero prefiltrar el contenido utilizando la búsqueda de información de activos de alto nivel, tales como metadatos y etiquetas, ya sea reconocido por el sistema de proporcionado por el usuario.</t>
   </si>
   <si>
     <t>Como administrador de Zooniverse, quiero evaluar lo interesante o atractivo o complejo que es un cuadro basado en análisis automatizado, anotaciones ciudadanas y comentarios sobre Talk.</t>
@@ -460,12 +456,80 @@
   <si>
     <t>EVALUACION RAPIDA DEL MATERIAL DE AUDIO EDITADO</t>
   </si>
+  <si>
+    <t xml:space="preserve">PREFILTRAR </t>
+  </si>
+  <si>
+    <t>CONTENIDO DE LA DESNUDEZ</t>
+  </si>
+  <si>
+    <t>CONTENIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAR </t>
+  </si>
+  <si>
+    <t>CONTENIDOS INGERIDOS</t>
+  </si>
+  <si>
+    <r>
+      <t>Como</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> administrador</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, quiero </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prefiltrar el contenido</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> utilizando la búsqueda de información de activos de alto nivel, tales como metadatos y etiquetas, ya sea reconocido por el sistema de proporcionado por el usuario.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">EVALUAR </t>
+  </si>
+  <si>
+    <t>CUADRO BASADO EN ANALISIS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,6 +562,14 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -889,34 +961,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -924,22 +996,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -950,22 +1022,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -976,22 +1048,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -1002,22 +1074,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -1028,22 +1100,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -1054,22 +1126,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -1080,22 +1152,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1106,22 +1178,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1132,22 +1204,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -1158,22 +1230,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1184,22 +1256,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1210,22 +1282,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1236,22 +1308,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1262,22 +1334,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1288,22 +1360,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1314,22 +1386,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1340,22 +1412,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1366,22 +1438,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1392,22 +1464,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1418,22 +1490,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1444,22 +1516,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -1470,22 +1542,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="G23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1496,15 +1568,23 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="8"/>
+      <c r="D24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -1514,15 +1594,23 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="D25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1532,15 +1620,23 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="D26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1550,15 +1646,23 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1568,15 +1672,23 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1586,10 +1698,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="4"/>
@@ -1604,10 +1716,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="4"/>
@@ -1622,10 +1734,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="4"/>
@@ -1640,10 +1752,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="4"/>
@@ -1658,10 +1770,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="4"/>
@@ -1676,10 +1788,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
@@ -1694,10 +1806,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
@@ -1712,10 +1824,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4"/>
@@ -1730,10 +1842,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4"/>
@@ -1748,10 +1860,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
@@ -1766,10 +1878,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4"/>
@@ -1784,10 +1896,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4"/>
@@ -1802,10 +1914,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="4"/>
@@ -1820,10 +1932,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
@@ -1838,10 +1950,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="4"/>
@@ -1856,10 +1968,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
@@ -1874,10 +1986,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="4"/>
@@ -1892,10 +2004,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="4"/>
@@ -1910,10 +2022,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="4"/>
@@ -1928,10 +2040,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="4"/>
@@ -1946,10 +2058,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="4"/>
@@ -1964,10 +2076,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="4"/>
@@ -1982,10 +2094,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="4"/>
@@ -2000,10 +2112,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
@@ -2018,10 +2130,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="4"/>
@@ -2036,10 +2148,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
@@ -2054,10 +2166,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
@@ -2072,10 +2184,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
@@ -2090,10 +2202,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="4"/>
@@ -2108,10 +2220,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="4"/>
@@ -2126,10 +2238,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="4"/>
@@ -2144,10 +2256,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="4"/>
@@ -2162,10 +2274,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="4"/>

--- a/Libro1(Recuperado automáticamente).xlsx
+++ b/Libro1(Recuperado automáticamente).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CIST\Downloads\Selene-PFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37F084B-6C66-4D74-A006-2042BE022F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98E87AC-B070-4F2B-8531-6F71CBCA131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EBE5DF2-C0CF-4ED1-8D2B-CD3E00818B64}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="153">
   <si>
     <t>Como usuario, quiero buscar y descubrir música basada en mi perfil.</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>Como administrador de Zooniverse, quiero realizar la reclasificación automática de especies animales en Snapshot Serengeti.</t>
-  </si>
-  <si>
-    <t>Como administrador Zooniverse, quiero realizar automáticamente atributo animal p reclasificación en Snapshot Serengeti.</t>
   </si>
   <si>
     <t>Como administrador de Zooniverse, quiero realizar la detección automática de números de animales en Snapshot Serengeti.</t>
@@ -523,6 +520,105 @@
   </si>
   <si>
     <t>CUADRO BASADO EN ANALISIS</t>
+  </si>
+  <si>
+    <t>DETECTAR</t>
+  </si>
+  <si>
+    <t>PRECLASIFICAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUANDO UN CIENTIFICO DEBE SER INVITADO </t>
+  </si>
+  <si>
+    <t>TIPOS DE VOLUNTARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMÁGENES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMÁGENES DE SNAPSHOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REALIZAR </t>
+  </si>
+  <si>
+    <t>DETECCION AUTOMATICA DE SERIES DE IMÁGENES</t>
+  </si>
+  <si>
+    <t>RECLASIFICACION AUTOMATICA</t>
+  </si>
+  <si>
+    <t>Como administrador de Zooniverse, quiero realizar una preclasificación automática de especies animales en Snapshot Serengeti.</t>
+  </si>
+  <si>
+    <t>PRECLASIFICACION AUTOMATICA DE ESPECIES DE ANIMALES</t>
+  </si>
+  <si>
+    <t>DETECCION AUTOMATICA DE NUMEROS DE ANIMALES</t>
+  </si>
+  <si>
+    <t>SEGMENTACION O LOCALIZACION AUTOMATICA DEL PLANCTON EN EL PORTAL DE PLANCTON</t>
+  </si>
+  <si>
+    <t>IMÁGENES DEL PORTAL DE PLANCTON SIN PLACTON CLASIFICABLE EN ELLAS</t>
+  </si>
+  <si>
+    <t>DETECCION AUTOMATICA DEL TAMAÑO O LA ORIENTACION ..</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECLASIFICACION AUTOMATICA </t>
+  </si>
+  <si>
+    <t>ANALISIS AUTOMATICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMATICAMENTE EL TIEMPO EN UN VIDEO </t>
+  </si>
+  <si>
+    <t>CARACTERISTICAS IMPORTANTES COMO AREAS DE INUNDACION</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD/PESO DE UNA CLASIFICACION VOLUNTARIA BASADA EN SU EXPERIENCIA</t>
+  </si>
+  <si>
+    <t>AGRUPAR</t>
+  </si>
+  <si>
+    <t>SABER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREFILTRADO DE LAS IMÁGENES PARA ELIMINAR </t>
+  </si>
+  <si>
+    <t>OBJETOS MOVILES Y TRANSITORIOS EN LAS IMÁGENES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIMINAR </t>
+  </si>
+  <si>
+    <t>RUIDO DE FONDO Y DISTRAER LOS SONIDOS DE LOS ARCHIVOS DE AUDIO</t>
+  </si>
+  <si>
+    <t>LLAMADAS DE BALLENA QUE SON SIMILARES</t>
+  </si>
+  <si>
+    <t>NUMERO DE BALLENAS ESCUCHADAS EN UN SOLO ARCHIVO DE AUDIO</t>
+  </si>
+  <si>
+    <t>CUANDO DEBERIA INTERRUMPIR A UN VOLUNTARIO</t>
+  </si>
+  <si>
+    <t>saber</t>
+  </si>
+  <si>
+    <t>si debo interrumpir a un voluntario con texto</t>
+  </si>
+  <si>
+    <t>cuando debo educar a un voluntario</t>
+  </si>
+  <si>
+    <t>SI DEBO EDUCAR A UN VOLUNTARIO CON TEXTO, UNA IMAGEN O UN VIDEO</t>
   </si>
 </sst>
 </file>
@@ -610,7 +706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -632,6 +728,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -955,40 +1055,41 @@
     <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="44.88671875" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="2"/>
-    <col min="6" max="10" width="17.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27" style="2" customWidth="1"/>
+    <col min="7" max="10" width="17.44140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -996,22 +1097,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -1022,22 +1123,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1048,22 +1149,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -1074,22 +1175,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -1100,22 +1201,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -1126,22 +1227,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -1152,22 +1253,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1178,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1204,22 +1305,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -1230,22 +1331,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1256,22 +1357,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1282,22 +1383,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1308,22 +1409,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1334,22 +1435,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1360,22 +1461,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1386,22 +1487,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1412,22 +1513,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1438,22 +1539,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1464,22 +1565,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1490,22 +1591,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1516,22 +1617,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -1542,22 +1643,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="G23" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1568,22 +1669,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="G24" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1594,22 +1695,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1620,22 +1721,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="G26" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -1646,22 +1747,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1672,22 +1773,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="G28" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1698,15 +1799,23 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="D29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -1716,15 +1825,23 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="D30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1734,15 +1851,23 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="D31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -1752,15 +1877,23 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="D32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1770,15 +1903,23 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="D33" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -1788,33 +1929,49 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="D34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -1824,33 +1981,49 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -1860,15 +2033,23 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -1878,15 +2059,23 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -1896,15 +2085,23 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -1914,15 +2111,23 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -1932,15 +2137,23 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -1950,15 +2163,23 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -1968,15 +2189,23 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -1986,33 +2215,49 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2022,15 +2267,23 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2040,15 +2293,23 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -2058,33 +2319,49 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2094,15 +2371,23 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -2112,15 +2397,23 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -2130,15 +2423,23 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -2148,14 +2449,18 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F54" s="8"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -2166,10 +2471,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
@@ -2184,10 +2489,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
@@ -2202,10 +2507,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="4"/>
@@ -2220,10 +2525,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="4"/>
@@ -2238,10 +2543,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="4"/>
@@ -2256,10 +2561,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="4"/>
@@ -2274,10 +2579,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="4"/>

--- a/Libro1(Recuperado automáticamente).xlsx
+++ b/Libro1(Recuperado automáticamente).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CIST\Downloads\Selene-PFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98E87AC-B070-4F2B-8531-6F71CBCA131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E75850-2E15-4EC1-9ED7-93B4BFC026DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EBE5DF2-C0CF-4ED1-8D2B-CD3E00818B64}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="163">
   <si>
     <t>Como usuario, quiero buscar y descubrir música basada en mi perfil.</t>
   </si>
@@ -619,6 +619,36 @@
   </si>
   <si>
     <t>SI DEBO EDUCAR A UN VOLUNTARIO CON TEXTO, UNA IMAGEN O UN VIDEO</t>
+  </si>
+  <si>
+    <t>EDUCACION DEBO DAR A UN VOLUNTARIO</t>
+  </si>
+  <si>
+    <t>RECOMENDAR</t>
+  </si>
+  <si>
+    <t>CUANDO UN VOLUNTARIO  HA HECHO UN COMENTARIO INTERESANTE</t>
+  </si>
+  <si>
+    <t>PARA QUE LOS REUTILICE</t>
+  </si>
+  <si>
+    <t>CUANDO ZOONIBOT DEBE COMENTAR SOBRE UN TEMA</t>
+  </si>
+  <si>
+    <t>CUANDO ZOONIBOT DEBERIA DAR UNA EXPLICACION</t>
+  </si>
+  <si>
+    <t>LO QUE ZOONIBOT DEBERIA DECIRLE A UN VOLUNTARIO</t>
+  </si>
+  <si>
+    <t>SUJETOS POR SIMILITUD</t>
+  </si>
+  <si>
+    <t>DIFERENTES PROYECTOS A LOS VOLUNTARIOS EN FUNCION DE SUS EXPERIENCIAS ANTERIORES</t>
+  </si>
+  <si>
+    <t>RESUMEN DE LOS ARTICULOS</t>
   </si>
 </sst>
 </file>
@@ -706,7 +736,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -730,10 +760,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1144,7 +1171,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1222,7 +1249,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1248,7 +1275,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1274,7 +1301,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1300,7 +1327,7 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1508,7 +1535,7 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1612,7 +1639,7 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1638,7 +1665,7 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1908,7 +1935,7 @@
       <c r="C33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="3" t="s">
         <v>97</v>
       </c>
       <c r="E33" s="4" t="s">
@@ -1950,14 +1977,14 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -1986,7 +2013,7 @@
       <c r="C36" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="3" t="s">
         <v>97</v>
       </c>
       <c r="E36" s="4" t="s">
@@ -2460,8 +2487,12 @@
       <c r="E54" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="4"/>
+      <c r="F54" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -2476,10 +2507,18 @@
       <c r="C55" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
+      <c r="D55" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -2494,10 +2533,18 @@
       <c r="C56" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="D56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
@@ -2512,10 +2559,18 @@
       <c r="C57" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+      <c r="D57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
@@ -2530,10 +2585,18 @@
       <c r="C58" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
+      <c r="D58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
@@ -2548,15 +2611,23 @@
       <c r="C59" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
+      <c r="D59" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -2566,10 +2637,18 @@
       <c r="C60" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="D60" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
@@ -2584,10 +2663,18 @@
       <c r="C61" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
+      <c r="D61" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
